--- a/26.2.1.5_Test Status Report.xlsx
+++ b/26.2.1.5_Test Status Report.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Online Runs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve Runs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition Runs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1108,4 +1109,495 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Run Description</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>IMPSettlingDistance (m)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IMPSettlingTime (s)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SettlingDistance (m)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>SettlingTime (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Run 24 - acq_parallel_run9_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>31.479</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.479</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Run 25 - acq_parallel_run10_5mph_1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>49.651</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>49.651</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Run 26 - acq_parallel_run11_8mph_1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>38.549</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="D4" t="n">
+        <v>38.549</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Run 27 - acq_30dg_10ft_run12_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="C5" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Run 28 - acq_30dg_25ft_run13_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>37.572</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D6" t="n">
+        <v>37.572</v>
+      </c>
+      <c r="E6" t="n">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Run 29 - acq_30dg_10ft_run14_5mph_1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>28.769</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>28.769</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Run 30 - acq_30dg_25ft_run15_5mph_1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="C8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Run 31 - acq_30dg_10ft_run16_8mph_1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>44.239</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>44.239</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Run 32 - acq_30dg_25ft_run17_8mph_1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>56.173</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="D10" t="n">
+        <v>56.173</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Run 33 - acq_30dg_25ft_run13_accu_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>36.358</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22.95</v>
+      </c>
+      <c r="D11" t="n">
+        <v>27.678</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Run 34 - acq_30dg_10ft_run12_accu_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>28.714</v>
+      </c>
+      <c r="C12" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18.219</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Run 35 - acq_30dg_10ft_run14_accu_5mph_1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>30.357</v>
+      </c>
+      <c r="C13" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18.981</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8.65</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Run 36 - acq_30dg_25ft_run15_accu_5mph_1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>39.279</v>
+      </c>
+      <c r="C14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30.878</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Run 37 - acq_30dg_10ft_run16_accu_8mph_1</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>52.867</v>
+      </c>
+      <c r="C15" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>33.841</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Run 38 - acq_30dg_25ft_run17_accu_8mph_1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>37.505</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22.126</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Run 39 - acq_75dg_10ft_run18_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="C17" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>36.58</v>
+      </c>
+      <c r="E17" t="n">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Run 40 - acq_75dg_30ft_run19_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>44.359</v>
+      </c>
+      <c r="C18" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="D18" t="n">
+        <v>44.359</v>
+      </c>
+      <c r="E18" t="n">
+        <v>27.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Run 41 - acq_75dg_10ft_run20_5mph_1</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>39.656</v>
+      </c>
+      <c r="C19" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>39.656</v>
+      </c>
+      <c r="E19" t="n">
+        <v>18.15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Run 42 - acq_75dg_30ft_run21_5mph_1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>42.475</v>
+      </c>
+      <c r="C20" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>42.475</v>
+      </c>
+      <c r="E20" t="n">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Run 43 - acq_75dg_10ft_run18_accu_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>33.286</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="D21" t="n">
+        <v>26.835</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Run 44 - acq_75dg_30ft_run19_accu_3.6mph_1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>45.646</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>29.507</v>
+      </c>
+      <c r="E22" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Run 45 - acq_75dg_30ft_run_21_accu_5mph_1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>33.186</v>
+      </c>
+      <c r="C23" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12.95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Run 46 - acq_75dg_10ft_run_20_accu_5mph_1</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>35.471</v>
+      </c>
+      <c r="C24" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>27.841</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Run 47 - acq_75dg_30ft_run_21_accu_5mph_2</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>31.896</v>
+      </c>
+      <c r="E25" t="n">
+        <v>14.55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>